--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C016.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C016.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간 교육계획 수립 서식" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'연간 교육계획 수립 서식'!$A$4:$T$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'연간 교육계획 수립 서식'!$A$1:$T$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'연간 교육계획 수립 서식'!$A$1:$T$266</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,6 +65,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
@@ -81,12 +85,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,24 +107,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,6 +201,35 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_REF_C016_1" displayName="T_REF_C016_1" ref="A5:T65" headerRowCount="1">
+  <autoFilter ref="A5:T65"/>
+  <tableColumns count="20">
+    <tableColumn id="1" name="NO"/>
+    <tableColumn id="2" name="안전보건"/>
+    <tableColumn id="3" name="공정안전"/>
+    <tableColumn id="4" name="수급업체"/>
+    <tableColumn id="5" name="교육과정"/>
+    <tableColumn id="6" name="1월"/>
+    <tableColumn id="7" name="2월"/>
+    <tableColumn id="8" name="3월"/>
+    <tableColumn id="9" name="4월"/>
+    <tableColumn id="10" name="5월"/>
+    <tableColumn id="11" name="6월"/>
+    <tableColumn id="12" name="7월"/>
+    <tableColumn id="13" name="8월"/>
+    <tableColumn id="14" name="9월"/>
+    <tableColumn id="15" name="10월"/>
+    <tableColumn id="16" name="11월"/>
+    <tableColumn id="17" name="12월"/>
+    <tableColumn id="18" name="대상인원(명)"/>
+    <tableColumn id="19" name="교육방법(내·외부)"/>
+    <tableColumn id="20" name="비고"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -531,278 +556,1469 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>연간 교육계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>작성</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>검토</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>승인</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>안전보건</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>공정안전</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>수급업체</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>교육과정</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1월</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>4월</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>5월</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>6월</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>8월</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>9월</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>10월</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>11월</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>대상인원(명)</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>교육방법(내·외부)</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr"/>
-    </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr"/>
+      <c r="T6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="6" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr"/>
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr"/>
-      <c r="P10" s="7" t="inlineStr"/>
-      <c r="Q10" s="7" t="inlineStr"/>
-      <c r="R10" s="5">
-        <f>SUM(R5:R9)</f>
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr"/>
-      <c r="T10" s="7" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="6" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="6" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="6" t="inlineStr"/>
+      <c r="T11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="6" t="inlineStr"/>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="6" t="inlineStr"/>
+      <c r="T12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="6" t="inlineStr"/>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="6" t="inlineStr"/>
+      <c r="T13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="6" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="6" t="inlineStr"/>
+      <c r="T14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="6" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="6" t="inlineStr"/>
+      <c r="T15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="6" t="inlineStr"/>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="6" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="6" t="inlineStr"/>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="6" t="inlineStr"/>
+      <c r="T17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="6" t="inlineStr"/>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="6" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="6" t="inlineStr"/>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="6" t="inlineStr"/>
+      <c r="T19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr"/>
+      <c r="Q20" s="6" t="inlineStr"/>
+      <c r="R20" s="6" t="inlineStr"/>
+      <c r="S20" s="6" t="inlineStr"/>
+      <c r="T20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="6" t="inlineStr"/>
+      <c r="R21" s="6" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr"/>
+      <c r="T21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr"/>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="6" t="inlineStr"/>
+      <c r="R23" s="6" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr"/>
+      <c r="T23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="6" t="inlineStr"/>
+      <c r="R24" s="6" t="inlineStr"/>
+      <c r="S24" s="6" t="inlineStr"/>
+      <c r="T24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr"/>
+      <c r="T28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr"/>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr"/>
+      <c r="P30" s="6" t="inlineStr"/>
+      <c r="Q30" s="6" t="inlineStr"/>
+      <c r="R30" s="6" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr"/>
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr"/>
+      <c r="O32" s="6" t="inlineStr"/>
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="6" t="inlineStr"/>
+      <c r="R32" s="6" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr"/>
+      <c r="N33" s="6" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr"/>
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr"/>
+      <c r="N34" s="6" t="inlineStr"/>
+      <c r="O34" s="6" t="inlineStr"/>
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr"/>
+      <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr"/>
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr"/>
+      <c r="T35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr"/>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr"/>
+      <c r="O36" s="6" t="inlineStr"/>
+      <c r="P36" s="6" t="inlineStr"/>
+      <c r="Q36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr"/>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr"/>
+      <c r="P37" s="6" t="inlineStr"/>
+      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr"/>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr"/>
+      <c r="N38" s="6" t="inlineStr"/>
+      <c r="O38" s="6" t="inlineStr"/>
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr"/>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr"/>
+      <c r="P39" s="6" t="inlineStr"/>
+      <c r="Q39" s="6" t="inlineStr"/>
+      <c r="R39" s="6" t="inlineStr"/>
+      <c r="S39" s="6" t="inlineStr"/>
+      <c r="T39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr"/>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr"/>
+      <c r="O40" s="6" t="inlineStr"/>
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="6" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr"/>
+      <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="6" t="inlineStr"/>
+      <c r="R41" s="6" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr"/>
+      <c r="C42" s="6" t="inlineStr"/>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="6" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr"/>
+      <c r="O42" s="6" t="inlineStr"/>
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="6" t="inlineStr"/>
+      <c r="B43" s="6" t="inlineStr"/>
+      <c r="C43" s="6" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="6" t="inlineStr"/>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr"/>
+      <c r="O44" s="6" t="inlineStr"/>
+      <c r="P44" s="6" t="inlineStr"/>
+      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="6" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr"/>
+      <c r="C45" s="6" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr"/>
+      <c r="Q45" s="6" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr"/>
+      <c r="T45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr"/>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="6" t="inlineStr"/>
+      <c r="O46" s="6" t="inlineStr"/>
+      <c r="P46" s="6" t="inlineStr"/>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="6" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr"/>
+      <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="6" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr"/>
+      <c r="P47" s="6" t="inlineStr"/>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="6" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr"/>
+      <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr"/>
+      <c r="O48" s="6" t="inlineStr"/>
+      <c r="P48" s="6" t="inlineStr"/>
+      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="6" t="inlineStr"/>
+      <c r="B49" s="6" t="inlineStr"/>
+      <c r="C49" s="6" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr"/>
+      <c r="L49" s="6" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr"/>
+      <c r="P49" s="6" t="inlineStr"/>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="6" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr"/>
+      <c r="C50" s="6" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
+      <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="6" t="inlineStr"/>
+      <c r="O50" s="6" t="inlineStr"/>
+      <c r="P50" s="6" t="inlineStr"/>
+      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="6" t="inlineStr"/>
+      <c r="B51" s="6" t="inlineStr"/>
+      <c r="C51" s="6" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="6" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr"/>
+      <c r="P51" s="6" t="inlineStr"/>
+      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="6" t="inlineStr"/>
+      <c r="B52" s="6" t="inlineStr"/>
+      <c r="C52" s="6" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr"/>
+      <c r="O52" s="6" t="inlineStr"/>
+      <c r="P52" s="6" t="inlineStr"/>
+      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="6" t="inlineStr"/>
+      <c r="B53" s="6" t="inlineStr"/>
+      <c r="C53" s="6" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr"/>
+      <c r="P53" s="6" t="inlineStr"/>
+      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="6" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr"/>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr"/>
+      <c r="O54" s="6" t="inlineStr"/>
+      <c r="P54" s="6" t="inlineStr"/>
+      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="6" t="inlineStr"/>
+      <c r="B55" s="6" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr"/>
+      <c r="P55" s="6" t="inlineStr"/>
+      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr"/>
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr"/>
+      <c r="I56" s="6" t="inlineStr"/>
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="6" t="inlineStr"/>
+      <c r="O56" s="6" t="inlineStr"/>
+      <c r="P56" s="6" t="inlineStr"/>
+      <c r="Q56" s="6" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr"/>
+      <c r="S56" s="6" t="inlineStr"/>
+      <c r="T56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="6" t="inlineStr"/>
+      <c r="B57" s="6" t="inlineStr"/>
+      <c r="C57" s="6" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr"/>
+      <c r="L57" s="6" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr"/>
+      <c r="P57" s="6" t="inlineStr"/>
+      <c r="Q57" s="6" t="inlineStr"/>
+      <c r="R57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr"/>
+      <c r="T57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="6" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr"/>
+      <c r="C58" s="6" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr"/>
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr"/>
+      <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="6" t="inlineStr"/>
+      <c r="O58" s="6" t="inlineStr"/>
+      <c r="P58" s="6" t="inlineStr"/>
+      <c r="Q58" s="6" t="inlineStr"/>
+      <c r="R58" s="6" t="inlineStr"/>
+      <c r="S58" s="6" t="inlineStr"/>
+      <c r="T58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="6" t="inlineStr"/>
+      <c r="C59" s="6" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="6" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr"/>
+      <c r="P59" s="6" t="inlineStr"/>
+      <c r="Q59" s="6" t="inlineStr"/>
+      <c r="R59" s="6" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr"/>
+      <c r="T59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr"/>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
+      <c r="L60" s="6" t="inlineStr"/>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="6" t="inlineStr"/>
+      <c r="O60" s="6" t="inlineStr"/>
+      <c r="P60" s="6" t="inlineStr"/>
+      <c r="Q60" s="6" t="inlineStr"/>
+      <c r="R60" s="6" t="inlineStr"/>
+      <c r="S60" s="6" t="inlineStr"/>
+      <c r="T60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="6" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr"/>
+      <c r="C61" s="6" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr"/>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr"/>
+      <c r="P61" s="6" t="inlineStr"/>
+      <c r="Q61" s="6" t="inlineStr"/>
+      <c r="R61" s="6" t="inlineStr"/>
+      <c r="S61" s="6" t="inlineStr"/>
+      <c r="T61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="6" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr"/>
+      <c r="C62" s="6" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="6" t="inlineStr"/>
+      <c r="O62" s="6" t="inlineStr"/>
+      <c r="P62" s="6" t="inlineStr"/>
+      <c r="Q62" s="6" t="inlineStr"/>
+      <c r="R62" s="6" t="inlineStr"/>
+      <c r="S62" s="6" t="inlineStr"/>
+      <c r="T62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="6" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr"/>
+      <c r="C63" s="6" t="inlineStr"/>
+      <c r="D63" s="6" t="inlineStr"/>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr"/>
+      <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr"/>
+      <c r="N63" s="6" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr"/>
+      <c r="P63" s="6" t="inlineStr"/>
+      <c r="Q63" s="6" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr"/>
+      <c r="S63" s="6" t="inlineStr"/>
+      <c r="T63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr"/>
+      <c r="C64" s="6" t="inlineStr"/>
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
+      <c r="L64" s="6" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr"/>
+      <c r="N64" s="6" t="inlineStr"/>
+      <c r="O64" s="6" t="inlineStr"/>
+      <c r="P64" s="6" t="inlineStr"/>
+      <c r="Q64" s="6" t="inlineStr"/>
+      <c r="R64" s="6" t="inlineStr"/>
+      <c r="S64" s="6" t="inlineStr"/>
+      <c r="T64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="6" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr"/>
+      <c r="C65" s="6" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr"/>
+      <c r="P65" s="6" t="inlineStr"/>
+      <c r="Q65" s="6" t="inlineStr"/>
+      <c r="R65" s="6" t="inlineStr"/>
+      <c r="S65" s="6" t="inlineStr"/>
+      <c r="T65" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T9"/>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:L2"/>
-    <mergeCell ref="M2:T2"/>
     <mergeCell ref="G3:L3"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:L4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="M4:T4"/>
     <mergeCell ref="M3:T3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C016.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C016.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간 교육계획 수립 서식" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'연간 교육계획 수립 서식'!$A$1:$T$266</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'연간 교육계획 수립 서식'!$A$1:$T$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
